--- a/FROM25_MARGIN_2110.xlsx
+++ b/FROM25_MARGIN_2110.xlsx
@@ -1098,130 +1098,140 @@
       <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Запросить спецификацию / КП, потом решать</t>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 17:40</t>
+          <t>27.10.2026 07:00</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>386-076</t>
+          <t>0387200026026000085</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>ООО «Союзспецодежда»</t>
+          <t>Бюджетное учреждение Ханты-Мансийского Автономног…</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Ботинки с высокими берцами - 4 000 пар</t>
+          <t>Поставка отведения для электрокардиографии (кабель)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>44-ФЗ · Запрос котировок в электр…</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Bidzaar</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="n"/>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>102610</v>
+      </c>
       <c r="K10" s="9" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.591</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>678286.0273972603</v>
+        <v>36669</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>низкая (оценка)</t>
+          <t>оценка</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>нужна спецификация</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr"/>
+          <t>Медизделие — нужно РУ Росздравнадзора и совместимость с ЭК12Т (лучше оригинал НПП «Монитор», Таганрог — запросить цену у производителя/дилера). Преим…</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0387200026026000085</t>
+        </is>
+      </c>
       <c r="P10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Запросить спецификацию / КП, потом решать</t>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 13:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Сантехника/арматура</t>
+          <t>СС/видеонаблюдение</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>0154300014626000828</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>ООО «Ремонтно-механический завод»</t>
+          <t>Муниципальное Казённое учреждение «Служба Техниче…</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый (56-100)</t>
+          <t>Поставка шкафа телекоммуникационного</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Конкурентный отбор</t>
+          <t>44-ФЗ · Запрос котировок в электр…</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>ЭТП Торги РФ</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="J11" s="8" t="n">
-        <v>10474222</v>
+        <v>37559</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.1965999956846437</v>
+        <v>0.348</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>560777.4667024664</v>
+        <v>5410</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>низкая (оценка)</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>нужна спецификация</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr"/>
+          <t>Ограничение иностранного (ПП 1875) — российский шкаф (ЦМО, Hyperline РФ?, ЦМО в реестре) с записью в реестре. Требование крепления к столбу — уточнит…</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0154300014626000828</t>
+        </is>
+      </c>
       <c r="P11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="44" customHeight="1">
@@ -1230,32 +1240,32 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Идём только при подтверждённом наличии (10 дней)</t>
+          <t>Запросить спецификацию / КП, потом решать</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>26.10.2026 17:40</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Форма/снаряжение</t>
+          <t>Одежда/СИЗ</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>B1510261835045</t>
+          <t>386-076</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>АНО «Таврида.Арт»</t>
+          <t>ООО «Союзспецодежда»</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Поставка форменной одежды для сотрудников службы безопасности АНО "Таврида.Арт"</t>
+          <t>Ботинки с высокими берцами - 4 000 пар</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1265,26 +1275,24 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>4169750</v>
-      </c>
+          <t>Bidzaar</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="n"/>
       <c r="K12" s="9" t="n">
-        <v>0.1747946519575514</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>319214.8824657535</v>
+        <v>678286.0273972603</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>высокая (построчно)</t>
+          <t>низкая (оценка)</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>поставка 10 дней — нужен товар в наличии; оплата 30 дн. после приёмки; цены кофты, ботинок, жилета, перчаток — подтвердить КП</t>
+          <t>нужна спецификация</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr"/>
@@ -1311,7 +1319,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1321,7 +1329,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Запорная арматура</t>
+          <t>Затвор дисковый (56-100)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1335,13 +1343,13 @@
         </is>
       </c>
       <c r="J13" s="8" t="n">
-        <v>4248523</v>
+        <v>10474222</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.196600089019172</v>
+        <v>0.1965999956846437</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>227461.2483495892</v>
+        <v>560777.4667024664</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1362,37 +1370,37 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Запросить спецификацию / КП, потом решать</t>
+          <t>Идём только при подтверждённом наличии (10 дней)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>27.10.2026 10:00</t>
+          <t>30.10.2026 12:00</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Форма/снаряжение</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>32616484613</t>
+          <t>B1510261835045</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>АО «Объединенные Региональные Электрические Сети …</t>
+          <t>АНО «Таврида.Арт»</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>ОРЭСВО-4080 Поставка материалов для выполнения обязательств по договорам технологического…</t>
+          <t>Поставка форменной одежды для сотрудников службы безопасности АНО "Таврида.Арт"</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Другой тип конкурса</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1401,29 +1409,25 @@
         </is>
       </c>
       <c r="J14" s="8" t="n">
-        <v>3600000</v>
+        <v>4169750</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1747946519575514</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>203486</v>
+        <v>319214.8824657535</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>низкая (оценка)</t>
+          <t>высокая (построчно)</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Спецификация в архиве ОРЭСВО-4080.7z (zakupki.gov.ru). Конкурс — оценка не только цены. Связное оборудование под ПП 1875. Типовая маржа электросетевы…</t>
-        </is>
-      </c>
-      <c r="O14" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616484613</t>
-        </is>
-      </c>
+          <t>поставка 10 дней — нужен товар в наличии; оплата 30 дн. после приёмки; цены кофты, ботинок, жилета, перчаток — подтвердить КП</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr"/>
       <c r="P14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="44" customHeight="1">
@@ -1432,66 +1436,66 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Запросить спецификацию / КП, потом решать</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 11:00</t>
+          <t>26.10.2026 09:00</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>СС/видеонаблюдение</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>32616478334</t>
+          <t>0373100015726000144</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>АО «Россети Сибирь Тываэнерго»</t>
+          <t>Федеральное государственное Образовательное бюдже…</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Конкурс в электронной форме №26-59 на право заключение договора на поставку кабельных муф…</t>
+          <t>Поставка и монтаж, включая пусконаладочные работы, инженерно-технических средств (систем)…</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Конкурс в электронной фо…</t>
+          <t>44-ФЗ · Запрос котировок в электр…</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>ТЭК-Торг</t>
         </is>
       </c>
       <c r="J15" s="8" t="n">
-        <v>2579079</v>
+        <v>6586955.59</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.2000000775470624</v>
+        <v>0.223</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>145780</v>
+        <v>230166</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>низкая (оценка)</t>
+          <t>оценка</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>Номенклатура в «Документация ОК 26-59.7z»; доставка в Тыву дорогая; Россети — обычно конкуренция заводов-дилеров (ЗЭТ, Михнево, Нилед), маржа 15–25%.</t>
+          <t>Товары 2 920 289 ₽ (44,3%), работы 3 666 667 ₽ (55,7%) — монтаж/ПНР только через субподрядчика (СРО не требуется до 10 млн, но нужна бригада, ответст…</t>
         </is>
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616478334</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0373100015726000144</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr"/>
@@ -1507,47 +1511,47 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 09:00</t>
+          <t>26.10.2026 13:00</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Форма/снаряжение</t>
+          <t>Сантехника/арматура</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>32616476844</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>МАОУ «Нижнетавдинская СОШ»</t>
+          <t>ООО «Ремонтно-механический завод»</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Поставка оборудования для кабинета ОБЗР для нужд МАОУ «Нижнетавдинская СОШ».</t>
+          <t>Запорная арматура</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в элект…</t>
+          <t>Коммерческие · Конкурентный отбор</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>ЭТП Торги РФ</t>
         </is>
       </c>
       <c r="J16" s="8" t="n">
-        <v>576350.78</v>
+        <v>4248523</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.2239743303548579</v>
+        <v>0.196600089019172</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>44709</v>
+        <v>227461.2483495892</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1556,14 +1560,10 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Сборная номенклатура ~17 позиций, DJI-дрон (санкц./серый импорт), бронежилет, макеты мин; маржа оценочная ~22%</t>
-        </is>
-      </c>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616476844</t>
-        </is>
-      </c>
+          <t>нужна спецификация</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="44" customHeight="1">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 11:00</t>
+          <t>27.10.2026 10:00</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1587,37 +1587,37 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>32616482760</t>
+          <t>32616484613</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Федеральная Сетевая Компания - Россети»</t>
+          <t>АО «Объединенные Региональные Электрические Сети …</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Запрос котировок в электронной форме (МСП) на право заключения договора поставки материал…</t>
+          <t>ОРЭСВО-4080 Поставка материалов для выполнения обязательств по договорам технологического…</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в элект…</t>
+          <t>223-ФЗ · Другой тип конкурса</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="J17" s="8" t="n">
-        <v>1051902.06</v>
+        <v>3600000</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.1799997045352303</v>
+        <v>0.2</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>40987</v>
+        <v>203486</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>Состав только в Разделе 7 ТЗ; ПП 1875 приложение к ТЗ; изоляторы/арматура ВЛ 220–500 кВ — узкий рынок.</t>
+          <t>Спецификация в архиве ОРЭСВО-4080.7z (zakupki.gov.ru). Конкурс — оценка не только цены. Связное оборудование под ПП 1875. Типовая маржа электросетевы…</t>
         </is>
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616482760</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616484613</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 04:00</t>
+          <t>26.10.2026 11:00</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>32616481935</t>
+          <t>32616478334</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Федеральное государственное автономное Образовате…</t>
+          <t>АО «Россети Сибирь Тываэнерго»</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Запрос котировок в электронной форме № 561-26/кт/эф на поставку электротехнических матери…</t>
+          <t>Конкурс в электронной форме №26-59 на право заключение договора на поставку кабельных муф…</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в элект…</t>
+          <t>223-ФЗ · Конкурс в электронной фо…</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="J18" s="8" t="n">
-        <v>424042.48</v>
+        <v>2579079</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.2200003169493773</v>
+        <v>0.2000000775470624</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>31414</v>
+        <v>145780</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>НМЦК по обоснованию 561-26 (недоступно); электроустановочные изделия — маржа 15–25%.</t>
+          <t>Номенклатура в «Документация ОК 26-59.7z»; доставка в Тыву дорогая; Россети — обычно конкуренция заводов-дилеров (ЗЭТ, Михнево, Нилед), маржа 15–25%.</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616481935</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616478334</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr"/>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Запросить спецификацию / КП, потом решать</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 07:00</t>
+          <t>27.10.2026 15:00</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1727,51 +1727,51 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>32616477841</t>
+          <t>32616481688</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>МУП «Луганскгорсвет»</t>
+          <t>ПАО «Россети Сибирь»</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>поставка электроматериалов</t>
+          <t>Конкурс в электронной форме № 26-1204 на право заключения договора поставки материалов дл…</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа ра…</t>
+          <t>223-ФЗ · Конкурс в электронной фо…</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Российская электронная система торгов</t>
+          <t>Росэлторг (ЕЭТП)</t>
         </is>
       </c>
       <c r="J19" s="8" t="n">
-        <v>485643</v>
+        <v>4270000</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.2086779795034625</v>
+        <v>0.172</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>31150</v>
+        <v>136003</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>низкая (оценка)</t>
+          <t>оценка</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>Доставка в ЛНР, тип предохранителя неизвестен (диапазон маржи 5–30%).</t>
+          <t>Позиции/количества неизвестны (3 строки по 1 усл.ед.). Поставка в разные адреса по Красноярскому краю (DIFFERENT_PLACE) — логистика дорогая (заложено…</t>
         </is>
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477841</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616481688</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr"/>
@@ -1782,37 +1782,37 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Осторожно — малая маржа</t>
+          <t>Запросить спецификацию / КП, потом решать</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 05:00</t>
+          <t>26.10.2026 09:00</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ</t>
+          <t>Форма/снаряжение</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>0352500002526000089</t>
+          <t>32616476844</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>Бюджетное учреждение Омской обл. «Тевризское Доро…</t>
+          <t>МАОУ «Нижнетавдинская СОШ»</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066998)</t>
+          <t>Поставка оборудования для кабинета ОБЗР для нужд МАОУ «Нижнетавдинская СОШ».</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электр…</t>
+          <t>223-ФЗ · Запрос котировок в элект…</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1821,30 +1821,30 @@
         </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>498211.82</v>
+        <v>576350.78</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.1988628451247905</v>
+        <v>0.2239743303548579</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>27663.44842735345</v>
+        <v>44709</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>средняя–высокая</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr"/>
+          <t>низкая (оценка)</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>Сборная номенклатура ~17 позиций, DJI-дрон (санкц./серый импорт), бронежилет, макеты мин; маржа оценочная ~22%</t>
+        </is>
+      </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000089</t>
-        </is>
-      </c>
-      <c r="P20" s="10" t="inlineStr">
-        <is>
-          <t>http://www.rts-tender.ru</t>
-        </is>
-      </c>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616476844</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>26.10.2026 11:00</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1867,22 +1867,22 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>32616477523</t>
+          <t>32616482760</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>АО «Коми Тепловая Компания»</t>
+          <t>ПАО «Федеральная Сетевая Компания - Россети»</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Поставка оборудование для обеспечения видеонаблюдения на квартальной котельной с. Стороже…</t>
+          <t>Запрос котировок в электронной форме (МСП) на право заключения договора поставки материал…</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа ра…</t>
+          <t>223-ФЗ · Запрос котировок в элект…</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>210371.75</v>
+        <v>1051902.06</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.2499991087206338</v>
+        <v>0.1799997045352303</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>21126</v>
+        <v>40987</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1906,82 +1906,82 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>Количества камер неизвестны (наборы); ПП 1875 — реестровое оборудование; Коми — доставка.</t>
+          <t>Состав только в Разделе 7 ТЗ; ПП 1875 приложение к ТЗ; изоляторы/арматура ВЛ 220–500 кВ — узкий рынок.</t>
         </is>
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477523</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="inlineStr">
-        <is>
-          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4065108</t>
-        </is>
-      </c>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616482760</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>Посчитать по позициям</t>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 09:00</t>
+          <t>26.10.2026 14:00</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>СС/видеонаблюдение</t>
+          <t>Сантехника/арматура</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>0373100015726000144</t>
+          <t>32616476122</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>Федеральное государственное Образовательное бюдже…</t>
+          <t>АО «Татэнерго»</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Поставка и монтаж, включая пусконаладочные работы, инженерно-технических средств (систем)…</t>
+          <t>Поставка арматуры трубопроводной запорной (для ремонта хозяйственным способом) для нужд ф…</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электр…</t>
+          <t>223-ФЗ · Закупка иного способа ра…</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>ТЭК-Торг</t>
+          <t>ZakazRF (АГЗРТ)</t>
         </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>6586955.59</v>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 15–20%</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="n"/>
+        <v>1286601.25</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>32573</v>
+      </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr"/>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>Спецификация НЕ получена — нужен ТЗ (Прил.1) и Прил.4 испр. Нацрежим: constraintNationalRegime=true (ПП 1875, ограничение — ЗРА только российская/ЕАЭ…</t>
+        </is>
+      </c>
       <c r="O22" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0373100015726000144</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616476122</t>
         </is>
       </c>
       <c r="P22" s="6" t="inlineStr"/>
@@ -1990,14 +1990,14 @@
       <c r="A23" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Посчитать по позициям</t>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Запросить спецификацию / КП, потом решать</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>27.10.2026 11:00</t>
+          <t>26.10.2026 04:00</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -2007,47 +2007,51 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>32616481688</t>
+          <t>32616481935</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Россети Сибирь»</t>
+          <t>Федеральное государственное автономное Образовате…</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Конкурс в электронной форме № 26-1204 на право заключения договора поставки материалов дл…</t>
+          <t>Запрос котировок в электронной форме № 561-26/кт/эф на поставку электротехнических матери…</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Конкурс в электронной фо…</t>
+          <t>223-ФЗ · Запрос котировок в элект…</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>4270000</v>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 10–15%</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="n"/>
+        <v>424042.48</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.2200003169493773</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>31414</v>
+      </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr"/>
+          <t>низкая (оценка)</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК по обоснованию 561-26 (недоступно); электроустановочные изделия — маржа 15–25%.</t>
+        </is>
+      </c>
       <c r="O23" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616481688</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616481935</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr"/>
@@ -2056,101 +2060,109 @@
       <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>Посчитать по позициям</t>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Запросить спецификацию / КП, потом решать</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>14.07.2027 10:00</t>
+          <t>26.10.2026 07:00</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Медрасходники (пробирки)</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>332598</t>
+          <t>32616477841</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>Частное учреждение Здравоохранения «Клиническая Б…</t>
+          <t>МУП «Луганскгорсвет»</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Поставка расходных медицинских материалов</t>
+          <t>поставка электроматериалов</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>223-ФЗ · Закупка иного способа ра…</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>РЖД-Медицина</t>
+          <t>Российская электронная система торгов</t>
         </is>
       </c>
       <c r="J24" s="8" t="n">
-        <v>1034883</v>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 30–50%</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="n"/>
+        <v>485643</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.2086779795034625</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>31150</v>
+      </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr"/>
-      <c r="O24" s="6" t="inlineStr"/>
+          <t>низкая (оценка)</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>Доставка в ЛНР, тип предохранителя неизвестен (диапазон маржи 5–30%).</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477841</t>
+        </is>
+      </c>
       <c r="P24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Посчитать по позициям</t>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Осторожно — малая маржа</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 10:00</t>
+          <t>26.10.2026 05:00</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Одежда/СИЗ</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>32616478568</t>
+          <t>0352500002526000089</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>МУП «Коломенский Трамвай»</t>
+          <t>Бюджетное учреждение Омской обл. «Тевризское Доро…</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Поставка силового бронированного кабеля для городского электрифицированного транспорта АС…</t>
+          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066998)</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа ра…</t>
+          <t>44-ФЗ · Запрос котировок в электр…</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2159,64 +2171,68 @@
         </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>956970.6</v>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 10–15%</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="n"/>
+        <v>498211.82</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.1988628451247905</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>27663.44842735345</v>
+      </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
+          <t>средняя–высокая</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr"/>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616478568</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr"/>
+          <t>https://zakupki.gov.ru/epz/order/notice/zk20/view/common-info.html?regNumber=0352500002526000089</t>
+        </is>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>http://www.rts-tender.ru</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Посчитать по позициям</t>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Запросить спецификацию / КП, потом решать</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>27.10.2026 09:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>СИЗ (респираторы)</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>4067730</t>
+          <t>32616477523</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>АО «Рждстрой»</t>
+          <t>АО «Коми Тепловая Компания»</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Запрос котировок в электронной форме № 31/ЗКТЭ-АО "РЖДстрой"/2026 на право заключения дог…</t>
+          <t>Поставка оборудование для обеспечения видеонаблюдения на квартальной котельной с. Стороже…</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос котировок</t>
+          <t>223-ФЗ · Закупка иного способа ра…</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -2225,30 +2241,42 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 20–30%</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="n"/>
+        <v>210371.75</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.2499991087206338</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>21126</v>
+      </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="inlineStr"/>
-      <c r="O26" s="6" t="inlineStr"/>
-      <c r="P26" s="6" t="inlineStr"/>
+          <t>низкая (оценка)</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>Количества камер неизвестны (наборы); ПП 1875 — реестровое оборудование; Коми — доставка.</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477523</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>https://223.rts-tender.ru/supplier/auction/Trade/View.aspx?Id=4065108</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>Посчитать по позициям</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -2289,18 +2317,22 @@
       <c r="J27" s="8" t="n">
         <v>113094</v>
       </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 15–25%</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="n"/>
+      <c r="K27" s="9" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>664</v>
+      </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr"/>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>Спецификация (DN/Ру/тип) в архиве .rar на ЕИС — недоступен; оценка по Ду100. Нацрежим: ограничение (constraintNationalRegime=true) — нужна российская…</t>
+        </is>
+      </c>
       <c r="O27" s="10" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616451568</t>
@@ -2319,32 +2351,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 18:11</t>
+          <t>02.11.2026 10:00</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Медрасходники (пробирки)</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>10731867</t>
+          <t>32616478568</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>ГБУЗ «Онкологический Центр Калининградской Област…</t>
+          <t>МУП «Коломенский Трамвай»</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>на поставку изделий медицинского назначения для нужд Государственного бюджетного учрежден…</t>
+          <t>Поставка силового бронированного кабеля для городского электрифицированного транспорта АС…</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Малые закупки · Малая закупка</t>
+          <t>223-ФЗ · Закупка иного способа ра…</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -2353,11 +2385,11 @@
         </is>
       </c>
       <c r="J28" s="8" t="n">
-        <v>104898.65</v>
+        <v>956970.6</v>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>ориентир 30–50%</t>
+          <t>ориентир 10–15%</t>
         </is>
       </c>
       <c r="L28" s="8" t="n"/>
@@ -2367,7 +2399,11 @@
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr"/>
-      <c r="O28" s="6" t="inlineStr"/>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616478568</t>
+        </is>
+      </c>
       <c r="P28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="44" customHeight="1">
@@ -2376,64 +2412,60 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>Посчитать по позициям</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>27.10.2026 07:00</t>
+          <t>27.10.2026 09:00</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>СИЗ (респираторы)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>0387200026026000085</t>
+          <t>4067730</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>Бюджетное учреждение Ханты-Мансийского Автономног…</t>
+          <t>АО «Рждстрой»</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Поставка отведения для электрокардиографии (кабель)</t>
+          <t>Запрос котировок в электронной форме № 31/ЗКТЭ-АО "РЖДстрой"/2026 на право заключения дог…</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электр…</t>
+          <t>Коммерческие · Запрос котировок</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>102610</v>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 10–15%</t>
-        </is>
-      </c>
+        <v>120000</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr"/>
       <c r="L29" s="8" t="n"/>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="inlineStr"/>
-      <c r="O29" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0387200026026000085</t>
-        </is>
-      </c>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>Позиции неизвестны (респираторы/СИЗ?). Малый лот 120 т.р.: при типичной марже СИЗ 20–30% net ≈ 10–20 т.р. Для СИЗ — российские производители (ПП 1875…</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="44" customHeight="1">
@@ -2442,64 +2474,60 @@
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>Посчитать по позициям</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>30.10.2026 18:11</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>СС/видеонаблюдение</t>
+          <t>Медрасходники (пробирки)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>0154300014626000828</t>
+          <t>10731867</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>Муниципальное Казённое учреждение «Служба Техниче…</t>
+          <t>ГБУЗ «Онкологический Центр Калининградской Област…</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Поставка шкафа телекоммуникационного</t>
+          <t>на поставку изделий медицинского назначения для нужд Государственного бюджетного учрежден…</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электр…</t>
+          <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>37559</v>
-      </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 15–20%</t>
-        </is>
-      </c>
+        <v>104898.65</v>
+      </c>
+      <c r="K30" s="6" t="inlineStr"/>
       <c r="L30" s="8" t="n"/>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr"/>
-      <c r="O30" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0154300014626000828</t>
-        </is>
-      </c>
+          <t>оценка</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>Номенклатура неизвестна; медизделия требуют РУ, по 44-ФЗ (малая закупка по п.4/5 ч.1 ст.93) действует ПП 1875 — нужен российский товар. Калининград —…</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="44" customHeight="1">
@@ -3104,12 +3132,12 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Запросить спецификацию → КП</t>
+          <t>КП без обязательств (сбор цен)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>09.11.2026 13:30</t>
+          <t>28.10.2026 23:59</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -3119,27 +3147,27 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>249682</t>
+          <t>3506557</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Фосагро»</t>
+          <t>АО «Росатом Возобновляемая Энергия»</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Поставка лаб. посуды с фикс-й цены на 2027-28 г. для ГК "ФОСАГРО"</t>
+          <t>Поставка ТМЦ АХН (товарно-материальных ценностей административно-хозяйственного назначени…</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Мониторинг цен</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>ФосАгро</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="J40" s="8" t="n"/>
@@ -3156,7 +3184,7 @@
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+          <t>не закупка — участие в формировании НМЦК</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr"/>
@@ -3173,43 +3201,43 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>09.11.2026 13:30</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Медрасходники (пробирки)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>ЗП6101627</t>
+          <t>249682</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>ООО «Зарубежнефть-Добыча Харьяга»</t>
+          <t>ПАО «Фосагро»</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>ЗК-0241-26-МТ_Поставка кабельных муфт</t>
+          <t>Поставка лаб. посуды с фикс-й цены на 2027-28 г. для ГК "ФОСАГРО"</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос котировок</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>ТЭК-Торг</t>
+          <t>ФосАгро</t>
         </is>
       </c>
       <c r="J41" s="8" t="n"/>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>ориентир 10–15%</t>
+          <t>ориентир 30–50%</t>
         </is>
       </c>
       <c r="L41" s="8" t="n"/>
@@ -3237,43 +3265,43 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 17:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Соль</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>30337</t>
+          <t>ЗП6101627</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>АО «Новошахтинский Завод Нефтепродуктов»</t>
+          <t>ООО «Зарубежнефть-Добыча Харьяга»</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Химические соединения, реактивы, химикаты различного назначения</t>
+          <t>ЗК-0241-26-МТ_Поставка кабельных муфт</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос предложений</t>
+          <t>Коммерческие · Запрос котировок</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>АО «НЗНП МЕНЕДЖМЕНТ»</t>
+          <t>ТЭК-Торг</t>
         </is>
       </c>
       <c r="J42" s="8" t="n"/>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>ориентир 20–40%</t>
+          <t>ориентир 10–15%</t>
         </is>
       </c>
       <c r="L42" s="8" t="n"/>
@@ -3301,7 +3329,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>09.11.2026 13:30</t>
+          <t>26.10.2026 17:00</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -3311,27 +3339,27 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>249702</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Фосагро»</t>
+          <t>АО «Новошахтинский Завод Нефтепродуктов»</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Поставка хим. реактивов с фикс-й цены на 2027-28 г. для ГК "ФОСАГРО"</t>
+          <t>Химические соединения, реактивы, химикаты различного назначения</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>ФосАгро</t>
+          <t>АО «НЗНП МЕНЕДЖМЕНТ»</t>
         </is>
       </c>
       <c r="J43" s="8" t="n"/>
@@ -3360,44 +3388,48 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>КП без обязательств (сбор цен)</t>
+          <t>Запросить спецификацию → КП</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 17:00</t>
+          <t>09.11.2026 13:30</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Форма/снаряжение</t>
+          <t>Соль</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>20060526/1</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr"/>
+          <t>249702</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>ПАО «Фосагро»</t>
+        </is>
+      </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Укрывные материалы (ЗК октября)</t>
+          <t>Поставка хим. реактивов с фикс-й цены на 2027-28 г. для ГК "ФОСАГРО"</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>ТЭК-Торг</t>
+          <t>ФосАгро</t>
         </is>
       </c>
       <c r="J44" s="8" t="n"/>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>ориентир 25–35%</t>
+          <t>ориентир 20–40%</t>
         </is>
       </c>
       <c r="L44" s="8" t="n"/>
@@ -3408,7 +3440,7 @@
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>не закупка — участие в формировании НМЦК</t>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr"/>
@@ -3420,48 +3452,44 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Запросить спецификацию → КП</t>
+          <t>КП без обязательств (сбор цен)</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>04.11.2026 12:00</t>
+          <t>26.10.2026 17:00</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>СИЗ (респираторы)</t>
+          <t>Форма/снаряжение</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>386-334</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>ООО «ТД «Доминант»</t>
-        </is>
-      </c>
+          <t>20060526/1</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>СИЗ годовая потребность 2027</t>
+          <t>Укрывные материалы (ЗК октября)</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Запрос цен</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Bidzaar</t>
+          <t>ТЭК-Торг</t>
         </is>
       </c>
       <c r="J45" s="8" t="n"/>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>ориентир 20–30%</t>
+          <t>ориентир 25–35%</t>
         </is>
       </c>
       <c r="L45" s="8" t="n"/>
@@ -3472,7 +3500,7 @@
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+          <t>не закупка — участие в формировании НМЦК</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr"/>
@@ -3484,48 +3512,48 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>КП без обязательств (сбор цен)</t>
+          <t>Запросить спецификацию → КП</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 14:00</t>
+          <t>04.11.2026 12:00</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Сантехника/арматура</t>
+          <t>СИЗ (респираторы)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>0367200009326000852</t>
+          <t>386-334</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>ГБУЗ Тюменской обл. «Перинатальный Центр» (г.Тюме…</t>
+          <t>ООО «ТД «Доминант»</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Поставка трубы</t>
+          <t>СИЗ годовая потребность 2027</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>Bidzaar</t>
         </is>
       </c>
       <c r="J46" s="8" t="n"/>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>ориентир 15–25%</t>
+          <t>ориентир 20–30%</t>
         </is>
       </c>
       <c r="L46" s="8" t="n"/>
@@ -3536,14 +3564,10 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>не закупка — участие в формировании НМЦК</t>
-        </is>
-      </c>
-      <c r="O46" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0367200009326000852</t>
-        </is>
-      </c>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr"/>
       <c r="P46" s="6" t="inlineStr"/>
     </row>
     <row r="47" ht="44" customHeight="1">
@@ -3552,12 +3576,12 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>Запросить спецификацию → КП</t>
+          <t>КП без обязательств (сбор цен)</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>26.10.2026 14:00</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3567,27 +3591,27 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>7929</t>
+          <t>0367200009326000852</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>ООО «Рх-Снабжение»</t>
+          <t>ГБУЗ Тюменской обл. «Перинатальный Центр» (г.Тюме…</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Поставка ЗРА (РСУХ-3060)</t>
+          <t>Поставка трубы</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос оферт</t>
+          <t>44-ФЗ · Запрос цен</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>ЭТП Торги РФ</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="J47" s="8" t="n"/>
@@ -3604,10 +3628,14 @@
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
-        </is>
-      </c>
-      <c r="O47" s="6" t="inlineStr"/>
+          <t>не закупка — участие в формировании НМЦК</t>
+        </is>
+      </c>
+      <c r="O47" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0367200009326000852</t>
+        </is>
+      </c>
       <c r="P47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="44" customHeight="1">
@@ -3621,7 +3649,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>05.11.2026 13:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -3631,27 +3659,27 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>5518714</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>ЗАО «Магнитогорский завод прокатных валков»</t>
+          <t>ООО «Рх-Снабжение»</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Арматура, задвижка</t>
+          <t>Поставка ЗРА (РСУХ-3060)</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Запрос оферт</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>ЭТП ПАО ММК</t>
+          <t>ЭТП Торги РФ</t>
         </is>
       </c>
       <c r="J48" s="8" t="n"/>
@@ -3685,7 +3713,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 15:00</t>
+          <t>05.11.2026 13:00</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3695,27 +3723,27 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>4642960</t>
+          <t>5518714</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>Филиал «Вму» АО «Охк «Уралхим» в городе Воскресен…</t>
+          <t>ЗАО «Магнитогорский завод прокатных валков»</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Краны шаровые КШО по чертежам 64_26 СКЦ_КВ2026 ФВМУ</t>
+          <t>Арматура, задвижка</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Процедура закупки</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>ЭТП ПАО ММК</t>
         </is>
       </c>
       <c r="J49" s="8" t="n"/>
@@ -3744,12 +3772,12 @@
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>КП без обязательств (сбор цен)</t>
+          <t>Запросить спецификацию → КП</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 14:00</t>
+          <t>26.10.2026 15:00</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -3759,27 +3787,27 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>0367200009326000853</t>
+          <t>4642960</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>ГБУЗ Тюменской обл. «Перинатальный Центр» (г.Тюме…</t>
+          <t>Филиал «Вму» АО «Охк «Уралхим» в городе Воскресен…</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Поставка соединителей для трубы отопления</t>
+          <t>Краны шаровые КШО по чертежам 64_26 СКЦ_КВ2026 ФВМУ</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос цен</t>
+          <t>Коммерческие · Процедура закупки</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>ЕИС</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="J50" s="8" t="n"/>
@@ -3796,14 +3824,10 @@
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>не закупка — участие в формировании НМЦК</t>
-        </is>
-      </c>
-      <c r="O50" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0367200009326000853</t>
-        </is>
-      </c>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr"/>
       <c r="P50" s="6" t="inlineStr"/>
     </row>
     <row r="51" ht="44" customHeight="1">
@@ -3812,12 +3836,12 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Запросить спецификацию → КП</t>
+          <t>КП без обязательств (сбор цен)</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 13:00</t>
+          <t>26.10.2026 14:00</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -3827,27 +3851,27 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>5517846</t>
+          <t>0367200009326000853</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Магнитогорский Металлургический Комбинат»</t>
+          <t>ГБУЗ Тюменской обл. «Перинатальный Центр» (г.Тюме…</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>ТПА на 2027 часть 3</t>
+          <t>Поставка соединителей для трубы отопления</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>44-ФЗ · Запрос цен</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>ЭТП ПАО ММК</t>
+          <t>ЕИС</t>
         </is>
       </c>
       <c r="J51" s="8" t="n"/>
@@ -3864,10 +3888,14 @@
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
-        </is>
-      </c>
-      <c r="O51" s="6" t="inlineStr"/>
+          <t>не закупка — участие в формировании НМЦК</t>
+        </is>
+      </c>
+      <c r="O51" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0367200009326000853</t>
+        </is>
+      </c>
       <c r="P51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="44" customHeight="1">
@@ -3876,12 +3904,12 @@
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>КП без обязательств (сбор цен)</t>
+          <t>Запросить спецификацию → КП</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>29.10.2026 22:00</t>
+          <t>26.10.2026 13:00</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3891,27 +3919,27 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>1022240</t>
+          <t>5517846</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Тюменские Моторостроители»</t>
+          <t>ПАО «Магнитогорский Металлургический Комбинат»</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Сантехнические материалы: поставка 2027-2028г.</t>
+          <t>ТПА на 2027 часть 3</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>ЭТП ПАО ММК</t>
         </is>
       </c>
       <c r="J52" s="8" t="n"/>
@@ -3928,7 +3956,7 @@
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>не закупка — участие в формировании НМЦК</t>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
         </is>
       </c>
       <c r="O52" s="6" t="inlineStr"/>
@@ -3945,7 +3973,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>27.10.2026 23:59</t>
+          <t>29.10.2026 22:00</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -3955,27 +3983,27 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>3502254</t>
+          <t>1022240</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>АО «Атомстройэкспорт»</t>
+          <t>ПАО «Тюменские Моторостроители»</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Мониторинг цен по лоту № 1281287 «Поставка арматуры трубопроводной для сооружения энергоб…</t>
+          <t>Сантехнические материалы: поставка 2027-2028г.</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Мониторинг цен</t>
+          <t>Коммерческие · Запрос цен</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="J53" s="8" t="n"/>
@@ -4004,12 +4032,12 @@
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>Запросить спецификацию → КП</t>
+          <t>КП без обязательств (сбор цен)</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>27.10.2026 23:00</t>
+          <t>27.10.2026 23:59</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -4019,27 +4047,27 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>1253374</t>
+          <t>3502254</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Филиал ООО «Исо» (г Шелехов)</t>
+          <t>АО «Атомстройэкспорт»</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>закупка сантехники для филиала ООО ИСО в г. Шелехов</t>
+          <t>Мониторинг цен по лоту № 1281287 «Поставка арматуры трубопроводной для сооружения энергоб…</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Мониторинг цен</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>Тендер.Про</t>
+          <t>ЭТП «Фабрикант»</t>
         </is>
       </c>
       <c r="J54" s="8" t="n"/>
@@ -4056,7 +4084,7 @@
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+          <t>не закупка — участие в формировании НМЦК</t>
         </is>
       </c>
       <c r="O54" s="6" t="inlineStr"/>
@@ -4073,7 +4101,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>29.10.2026 23:00</t>
+          <t>27.10.2026 23:00</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -4083,17 +4111,17 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>1256610</t>
+          <t>1253374</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>Филиал ООО «Исо» (г Братск)</t>
+          <t>Филиал ООО «Исо» (г Шелехов)</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Закупка пневматики для электролизного производства филиалов ООО "ИСО" на 1 кв 2027 год</t>
+          <t>закупка сантехники для филиала ООО ИСО в г. Шелехов</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -4132,12 +4160,12 @@
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>КП без обязательств (сбор цен)</t>
+          <t>Запросить спецификацию → КП</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 03:25</t>
+          <t>29.10.2026 23:00</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -4147,27 +4175,27 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>4613430</t>
+          <t>1256610</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>АО «Нзму»</t>
+          <t>Филиал ООО «Исо» (г Братск)</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>ЗИП для ТОиР - Обзор рынка контрагентов поставки импортного оборудования и материалов</t>
+          <t>Закупка пневматики для электролизного производства филиалов ООО "ИСО" на 1 кв 2027 год</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>Тендер.Про</t>
         </is>
       </c>
       <c r="J56" s="8" t="n"/>
@@ -4184,7 +4212,7 @@
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>не закупка — участие в формировании НМЦК</t>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr"/>
@@ -4196,37 +4224,37 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>Запросить спецификацию → КП</t>
+          <t>КП без обязательств (сбор цен)</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 14:00</t>
+          <t>30.10.2026 03:25</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ</t>
+          <t>Сантехника/арматура</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>4644339</t>
+          <t>4613430</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>ООО «Слк Цемент»</t>
+          <t>АО «Нзму»</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>ЧАСТЬ2.Поставка спецодежды, спецобуви и СИЗ (ДСИЗ) работников Филиала «Коркино» ООО «СЛК …</t>
+          <t>ЗИП для ТОиР - Обзор рынка контрагентов поставки импортного оборудования и материалов</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос предложений</t>
+          <t>Коммерческие · Запрос цен</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -4237,7 +4265,7 @@
       <c r="J57" s="8" t="n"/>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>ориентир 25–35%</t>
+          <t>ориентир 15–25%</t>
         </is>
       </c>
       <c r="L57" s="8" t="n"/>
@@ -4248,7 +4276,7 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+          <t>не закупка — участие в формировании НМЦК</t>
         </is>
       </c>
       <c r="O57" s="6" t="inlineStr"/>
@@ -4265,7 +4293,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 09:00</t>
+          <t>02.11.2026 14:00</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -4275,27 +4303,27 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>c5ec6e</t>
+          <t>4644339</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>АО «Зеленодольский Молочноперерабатывающий Комбин…</t>
+          <t>ООО «Слк Цемент»</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>спецодежда</t>
+          <t>ЧАСТЬ2.Поставка спецодежды, спецобуви и СИЗ (ДСИЗ) работников Филиала «Коркино» ООО «СЛК …</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Коннектим</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="J58" s="8" t="n"/>
@@ -4329,7 +4357,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 12:00</t>
+          <t>26.10.2026 09:00</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -4339,27 +4367,27 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>4634447</t>
+          <t>c5ec6e</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>ООО «Биннофарм Групп»</t>
+          <t>АО «Зеленодольский Молочноперерабатывающий Комбин…</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Открытый запрос предложений по выбору ПУЛа поставщиков спецодежды для ГК Биннофарм Групп …</t>
+          <t>спецодежда</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос предложений</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>Коннектим</t>
         </is>
       </c>
       <c r="J59" s="8" t="n"/>
@@ -4393,7 +4421,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>26.10.2026 12:00</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -4403,27 +4431,27 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>387-052</t>
+          <t>4634447</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>АО «Евроцемент Груп»</t>
+          <t>ООО «Биннофарм Групп»</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Закупка спец. одежды для предприятия под индивидуальное изготовление</t>
+          <t>Открытый запрос предложений по выбору ПУЛа поставщиков спецодежды для ГК Биннофарм Групп …</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Bidzaar</t>
+          <t>B2B</t>
         </is>
       </c>
       <c r="J60" s="8" t="n"/>
@@ -4452,48 +4480,48 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>КП без обязательств (сбор цен)</t>
+          <t>Запросить спецификацию → КП</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 12:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>СС/видеонаблюдение</t>
+          <t>Одежда/СИЗ</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>4646711</t>
+          <t>387-052</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>ООО УК «Пмх»</t>
+          <t>АО «Евроцемент Груп»</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Комплектующие к оргтехнике</t>
+          <t>Закупка спец. одежды для предприятия под индивидуальное изготовление</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>B2B</t>
+          <t>Bidzaar</t>
         </is>
       </c>
       <c r="J61" s="8" t="n"/>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>ориентир 15–20%</t>
+          <t>ориентир 25–35%</t>
         </is>
       </c>
       <c r="L61" s="8" t="n"/>
@@ -4504,7 +4532,7 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>не закупка — участие в формировании НМЦК</t>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr"/>
@@ -4516,37 +4544,37 @@
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>Запросить спецификацию → КП</t>
+          <t>КП без обязательств (сбор цен)</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>06.11.2026 12:00</t>
+          <t>26.10.2026 12:00</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Вентиляция/фильтры</t>
+          <t>СС/видеонаблюдение</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>4646700</t>
+          <t>4646711</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>ООО «Лукойл-Транс»</t>
+          <t>ООО УК «Пмх»</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Поставка фильтров (топливных, воздушных, масляных)</t>
+          <t>Комплектующие к оргтехнике</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос предложений</t>
+          <t>Коммерческие · Запрос цен</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -4568,7 +4596,7 @@
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+          <t>не закупка — участие в формировании НМЦК</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr"/>
@@ -4578,70 +4606,64 @@
       <c r="A63" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>Не идём: Нет</t>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>Запросить спецификацию → КП</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 06:00</t>
+          <t>06.11.2026 12:00</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Вентиляция/фильтры</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>32616481886</t>
+          <t>4646700</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Стационарно…</t>
+          <t>ООО «Лукойл-Транс»</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Поставка оборудования и материалов</t>
+          <t>Поставка фильтров (топливных, воздушных, масляных)</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в элект…</t>
+          <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>РТС-тендер</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="n">
-        <v>272877.36</v>
-      </c>
-      <c r="K63" s="9" t="n">
-        <v>0.1800015948556524</v>
-      </c>
-      <c r="L63" s="8" t="n">
-        <v>10633</v>
-      </c>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>ориентир 15–20%</t>
+        </is>
+      </c>
+      <c r="L63" s="8" t="n"/>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>низкая (оценка)</t>
+          <t>нет НМЦК</t>
         </is>
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>Освещение с низкими ценами НМЦК (аналог лота Иваново); маржа ~15%.</t>
-        </is>
-      </c>
-      <c r="O63" s="10" t="inlineStr">
-        <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616481886</t>
-        </is>
-      </c>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr"/>
       <c r="P63" s="6" t="inlineStr"/>
     </row>
     <row r="64" ht="44" customHeight="1">
@@ -4655,32 +4677,32 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 10:00</t>
+          <t>26.10.2026 06:00</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>СС/видеонаблюдение</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>0371100005726000089</t>
+          <t>32616481886</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>Федеральное казенное учреждение «Исправительная к…</t>
+          <t>Государственное автономное учреждение Стационарно…</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Оборудование для оптимизации системы видеонаблюдения внутри учреждения</t>
+          <t>Поставка оборудования и материалов</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электр…</t>
+          <t>223-ФЗ · Запрос котировок в элект…</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
@@ -4689,13 +4711,13 @@
         </is>
       </c>
       <c r="J64" s="8" t="n">
-        <v>298225.45</v>
+        <v>272877.36</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.2016107277229359</v>
+        <v>0.1800015948556524</v>
       </c>
       <c r="L64" s="8" t="n">
-        <v>4705</v>
+        <v>10633</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4704,12 +4726,12 @@
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>ПП1875 по видеооборудованию (реестр РЭП) поднимает себестоимость камер; НМЦК камер 2,65 тыс — без запаса; ФКУ ИК — Рыбинск</t>
+          <t>Освещение с низкими ценами НМЦК (аналог лота Иваново); маржа ~15%.</t>
         </is>
       </c>
       <c r="O64" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0371100005726000089</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616481886</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr"/>
@@ -4720,62 +4742,66 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Не наш профиль</t>
+          <t>Не идём: Нет</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 10:00</t>
+          <t>26.10.2026 10:00</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Медрасходники (пробирки)</t>
+          <t>СС/видеонаблюдение</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>32616460692</t>
+          <t>0371100005726000089</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>ООО «Вторресурсхолдинг»</t>
+          <t>Федеральное казенное учреждение «Исправительная к…</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Поставка канцелярских товаров</t>
+          <t>Оборудование для оптимизации системы видеонаблюдения внутри учреждения</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа ра…</t>
+          <t>44-ФЗ · Запрос котировок в электр…</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>ЭТП ГПБ</t>
+          <t>РТС-тендер</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>ориентир 30–50%</t>
-        </is>
-      </c>
-      <c r="L65" s="8" t="n"/>
+        <v>298225.45</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.2016107277229359</v>
+      </c>
+      <c r="L65" s="8" t="n">
+        <v>4705</v>
+      </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>не посчитано</t>
-        </is>
-      </c>
-      <c r="N65" s="6" t="inlineStr"/>
+          <t>низкая (оценка)</t>
+        </is>
+      </c>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>ПП1875 по видеооборудованию (реестр РЭП) поднимает себестоимость камер; НМЦК камер 2,65 тыс — без запаса; ФКУ ИК — Рыбинск</t>
+        </is>
+      </c>
       <c r="O65" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616460692</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0371100005726000089</t>
         </is>
       </c>
       <c r="P65" s="6" t="inlineStr"/>
@@ -4791,7 +4817,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 12:00</t>
+          <t>28.10.2026 10:00</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -4801,31 +4827,31 @@
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>32616478499</t>
+          <t>32616460692</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Т Плюс»</t>
+          <t>ООО «Вторресурсхолдинг»</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Поставка "Канцелярские товары" для нужд филиала "Нижегородский" ПАО "Т Плюс"</t>
+          <t>Поставка канцелярских товаров</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Конкурс в электронной фо…</t>
+          <t>223-ФЗ · Закупка иного способа ра…</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЭТП ГПБ</t>
         </is>
       </c>
       <c r="J66" s="8" t="n">
-        <v>644005.45</v>
+        <v>1000000</v>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
@@ -4841,7 +4867,7 @@
       <c r="N66" s="6" t="inlineStr"/>
       <c r="O66" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616478499</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616460692</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr"/>
@@ -4857,45 +4883,45 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 07:00</t>
+          <t>26.10.2026 12:00</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Кабель (ЭОМ)</t>
+          <t>Медрасходники (пробирки)</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>32616477949</t>
+          <t>32616478499</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Здравоохран…</t>
+          <t>ПАО «Т Плюс»</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Поставка компьютерных комплектующих (камера, колонка, кабель)</t>
+          <t>Поставка "Канцелярские товары" для нужд филиала "Нижегородский" ПАО "Т Плюс"</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа ра…</t>
+          <t>223-ФЗ · Конкурс в электронной фо…</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>ЭТП Федерация закупок</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="J67" s="8" t="n">
-        <v>53329.95</v>
+        <v>644005.45</v>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>ориентир 10–15%</t>
+          <t>ориентир 30–50%</t>
         </is>
       </c>
       <c r="L67" s="8" t="n"/>
@@ -4907,7 +4933,7 @@
       <c r="N67" s="6" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477949</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616478499</t>
         </is>
       </c>
       <c r="P67" s="6" t="inlineStr"/>
@@ -4923,7 +4949,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 09:00</t>
+          <t>26.10.2026 07:00</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -4933,31 +4959,31 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>0372100049626002356</t>
+          <t>32616477949</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>Федеральное ГБУ «Национальный Медицинский Исследо…</t>
+          <t>Государственное автономное учреждение Здравоохран…</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Поставка монтажных ножей</t>
+          <t>Поставка компьютерных комплектующих (камера, колонка, кабель)</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электр…</t>
+          <t>223-ФЗ · Закупка иного способа ра…</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Сбербанк-АСТ</t>
+          <t>ЭТП Федерация закупок</t>
         </is>
       </c>
       <c r="J68" s="8" t="n">
-        <v>35424.36</v>
+        <v>53329.95</v>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
@@ -4973,7 +4999,7 @@
       <c r="N68" s="6" t="inlineStr"/>
       <c r="O68" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0372100049626002356</t>
+          <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616477949</t>
         </is>
       </c>
       <c r="P68" s="6" t="inlineStr"/>
@@ -4989,7 +5015,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 08:00</t>
+          <t>26.10.2026 09:00</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -4999,17 +5025,17 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>0360200049726000201</t>
+          <t>0372100049626002356</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>ГУЧ Здравоохранения «Областная Клиническая Психиа…</t>
+          <t>Федеральное ГБУ «Национальный Медицинский Исследо…</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Поставка стройматериалов</t>
+          <t>Поставка монтажных ножей</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -5019,11 +5045,11 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Росэлторг (ЕЭТП)</t>
+          <t>Сбербанк-АСТ</t>
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>25152.4</v>
+        <v>35424.36</v>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
@@ -5039,7 +5065,7 @@
       <c r="N69" s="6" t="inlineStr"/>
       <c r="O69" s="10" t="inlineStr">
         <is>
-          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0360200049726000201</t>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0372100049626002356</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr"/>
@@ -5055,57 +5081,59 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>26.10.2026 13:00</t>
+          <t>26.10.2026 08:00</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Медрасходники (пробирки)</t>
+          <t>Кабель (ЭОМ)</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>385-279</t>
+          <t>0360200049726000201</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>ООО «Интернет Решения»</t>
+          <t>ГУЧ Здравоохранения «Областная Клиническая Психиа…</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Сервис по обеспечению канцелярскими, хозяйственными и расходными материалами Ozon</t>
+          <t>Поставка стройматериалов</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>44-ФЗ · Запрос котировок в электр…</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Bidzaar</t>
-        </is>
-      </c>
-      <c r="J70" s="8" t="n"/>
+          <t>Росэлторг (ЕЭТП)</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>25152.4</v>
+      </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>ориентир 30–50%</t>
+          <t>ориентир 10–15%</t>
         </is>
       </c>
       <c r="L70" s="8" t="n"/>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>нет НМЦК</t>
-        </is>
-      </c>
-      <c r="N70" s="6" t="inlineStr">
-        <is>
-          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
-        </is>
-      </c>
-      <c r="O70" s="6" t="inlineStr"/>
+          <t>не посчитано</t>
+        </is>
+      </c>
+      <c r="N70" s="6" t="inlineStr"/>
+      <c r="O70" s="10" t="inlineStr">
+        <is>
+          <t>https://zakupki.gov.ru/epz/order/extendedsearch/results.html?searchString=0360200049726000201</t>
+        </is>
+      </c>
       <c r="P70" s="6" t="inlineStr"/>
     </row>
     <row r="71" ht="44" customHeight="1">
@@ -5119,7 +5147,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 23:59</t>
+          <t>26.10.2026 13:00</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -5129,27 +5157,27 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>3506557</t>
+          <t>385-279</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>АО «Росатом Возобновляемая Энергия»</t>
+          <t>ООО «Интернет Решения»</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Поставка ТМЦ АХН (товарно-материальных ценностей административно-хозяйственного назначени…</t>
+          <t>Сервис по обеспечению канцелярскими, хозяйственными и расходными материалами Ozon</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Коммерческие · Мониторинг цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>ЭТП «Фабрикант»</t>
+          <t>Bidzaar</t>
         </is>
       </c>
       <c r="J71" s="8" t="n"/>
@@ -5166,7 +5194,7 @@
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>не закупка — участие в формировании НМЦК</t>
+          <t>коммерческий запрос / без НМЦК — цена = наше КП</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
@@ -5594,40 +5622,41 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
